--- a/code/Created Files for Analysis/step2_pmm_robustness.xlsx
+++ b/code/Created Files for Analysis/step2_pmm_robustness.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -386,378 +386,378 @@
         <v>139</v>
       </c>
       <c r="C2">
-        <v>0.867</v>
+        <v>0.781</v>
       </c>
       <c r="D2">
-        <v>1.024</v>
+        <v>0.959</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WB-WDI-FM-AST-NFRG-CN</t>
+          <t>WB-WDI-EG-EGY-PRIM-PP-KD</t>
         </is>
       </c>
       <c r="B3">
-        <v>102</v>
+        <v>191</v>
       </c>
       <c r="C3">
-        <v>0.641</v>
+        <v>0.735</v>
       </c>
       <c r="D3">
-        <v>0.612</v>
+        <v>0.419</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WB-WDI-EG-EGY-PRIM-PP-KD</t>
+          <t>WB-WDI-GDP-ZG</t>
         </is>
       </c>
       <c r="B4">
-        <v>191</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>0.702</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="D4">
-        <v>0.394</v>
+        <v>0.374</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WB-WDI-TM-VAL-MMTL-ZS-UN</t>
+          <t>BN.CAB.XOKA.GD.ZS</t>
         </is>
       </c>
       <c r="B5">
-        <v>134</v>
+        <v>32</v>
       </c>
       <c r="C5">
-        <v>0.714</v>
+        <v>0.82</v>
       </c>
       <c r="D5">
-        <v>0.355</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BN.CAB.XOKA.GD.ZS</t>
+          <t>WB-WDI-TM-VAL-MMTL-ZS-UN</t>
         </is>
       </c>
       <c r="B6">
-        <v>32</v>
+        <v>134</v>
       </c>
       <c r="C6">
-        <v>0.846</v>
+        <v>0.729</v>
       </c>
       <c r="D6">
-        <v>0.269</v>
+        <v>0.311</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TT.PRI.MRCH.XD.WD</t>
+          <t>WB-WDI-NY-GDP-MKTP-KD</t>
         </is>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>0.211</v>
+        <v>0.394</v>
       </c>
       <c r="D7">
-        <v>0.268</v>
+        <v>0.285</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WB-WDI-NY-GDP-MKTP-KD</t>
+          <t>FP.CPI.TOTL.ZG</t>
         </is>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="C8">
-        <v>-0.331</v>
+        <v>0.257</v>
       </c>
       <c r="D8">
-        <v>0.221</v>
+        <v>0.251</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WB-WDI-SL-UEM-TOTL-NE-ZS</t>
+          <t>IMF-GDD-CG</t>
         </is>
       </c>
       <c r="B9">
-        <v>395</v>
+        <v>12</v>
       </c>
       <c r="C9">
-        <v>-0.002</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="D9">
-        <v>0.136</v>
+        <v>0.203</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FP.CPI.TOTL.ZG</t>
+          <t>TT.PRI.MRCH.XD.WD</t>
         </is>
       </c>
       <c r="B10">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C10">
-        <v>0.247</v>
+        <v>0.478</v>
       </c>
       <c r="D10">
-        <v>0.13</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UNDP-HDI-GII-LFPR-M</t>
+          <t>FS.AST.PRVT.GD.ZS</t>
         </is>
       </c>
       <c r="B11">
-        <v>24</v>
+        <v>182</v>
       </c>
       <c r="C11">
-        <v>-0.199</v>
+        <v>0.87</v>
       </c>
       <c r="D11">
-        <v>0.106</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WB-WDI-NE-EXP-GNFS-KD</t>
+          <t>WB-WDI-SL-EMP-1524-SP-NE-ZS</t>
         </is>
       </c>
       <c r="B12">
-        <v>113</v>
+        <v>498</v>
       </c>
       <c r="C12">
-        <v>0.917</v>
+        <v>0.863</v>
       </c>
       <c r="D12">
-        <v>0.102</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FS.AST.PRVT.GD.ZS</t>
+          <t>UNDP-HDI-GII-LFPR-F</t>
         </is>
       </c>
       <c r="B13">
-        <v>182</v>
+        <v>24</v>
       </c>
       <c r="C13">
-        <v>0.887</v>
+        <v>0.514</v>
       </c>
       <c r="D13">
-        <v>0.102</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WB-WDI-SL-EMP-1524-SP-NE-ZS</t>
+          <t>WB-CWON-PCA-PC</t>
         </is>
       </c>
       <c r="B14">
-        <v>498</v>
+        <v>445</v>
       </c>
       <c r="C14">
-        <v>0.868</v>
+        <v>0.966</v>
       </c>
       <c r="D14">
-        <v>0.073</v>
+        <v>0.079</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WB-CWON-PCA-PC</t>
+          <t>WB-WDI-NE-EXP-GNFS-KD</t>
         </is>
       </c>
       <c r="B15">
-        <v>445</v>
+        <v>113</v>
       </c>
       <c r="C15">
-        <v>0.956</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="D15">
-        <v>0.068</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WB-WDI-NE-CON-GOVT-CD</t>
+          <t>WB-WDI-NY-ADJ-DRES-GN-ZS</t>
         </is>
       </c>
       <c r="B16">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="C16">
-        <v>0.328</v>
+        <v>0.739</v>
       </c>
       <c r="D16">
-        <v>0.063</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FM.LBL.BMNY.GD.ZS</t>
+          <t>WB-WDI-SL-UEM-TOTL-NE-ZS</t>
         </is>
       </c>
       <c r="B17">
-        <v>94</v>
+        <v>395</v>
       </c>
       <c r="C17">
-        <v>-0.075</v>
+        <v>-0.024</v>
       </c>
       <c r="D17">
-        <v>0.051</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UNDP-HDI-GDI-GNI-PC-M</t>
+          <t>WB-WDI-NE-CON-GOVT-CD</t>
         </is>
       </c>
       <c r="B18">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="C18">
-        <v>0.408</v>
+        <v>0.035</v>
       </c>
       <c r="D18">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SWIID-GINI-MKT</t>
+          <t>UNDP-HDI-GDI-GNI-PC-M</t>
         </is>
       </c>
       <c r="B19">
-        <v>121</v>
+        <v>24</v>
       </c>
       <c r="C19">
-        <v>0.68</v>
+        <v>0.401</v>
       </c>
       <c r="D19">
-        <v>0.048</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WB-WDI-NY-ADJ-DRES-GN-ZS</t>
+          <t>SWIID-GINI-MKT</t>
         </is>
       </c>
       <c r="B20">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="C20">
-        <v>0.652</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="D20">
-        <v>0.039</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WB-WDI-BM-KLT-DINV-WD-GD-ZS</t>
+          <t>WB-WDI-TX-VAL-TECH-CD</t>
         </is>
       </c>
       <c r="B21">
-        <v>49</v>
+        <v>222</v>
       </c>
       <c r="C21">
-        <v>0.772</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="D21">
-        <v>0.037</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GC.XPN.TOTL.GD.ZS</t>
+          <t>WB-WDI-NE-GDI-TOTL-KD</t>
         </is>
       </c>
       <c r="B22">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="C22">
-        <v>0.8120000000000001</v>
+        <v>0.443</v>
       </c>
       <c r="D22">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WB-WDI-TX-VAL-TECH-CD</t>
+          <t>GC.XPN.TOTL.GD.ZS</t>
         </is>
       </c>
       <c r="B23">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="C23">
-        <v>0.582</v>
+        <v>0.885</v>
       </c>
       <c r="D23">
-        <v>0.034</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UNDP-HDI-GII-LFPR-F</t>
+          <t>WB-WDI-BM-KLT-DINV-WD-GD-ZS</t>
         </is>
       </c>
       <c r="B24">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C24">
-        <v>0.169</v>
+        <v>0.157</v>
       </c>
       <c r="D24">
-        <v>0.032</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>WB-WDI-NE-GDI-TOTL-KD</t>
+          <t>SWIID-GINI-DISP</t>
         </is>
       </c>
       <c r="B25">
-        <v>187</v>
+        <v>121</v>
       </c>
       <c r="C25">
-        <v>0.444</v>
+        <v>0.596</v>
       </c>
       <c r="D25">
-        <v>0.031</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="26">
@@ -770,122 +770,90 @@
         <v>284</v>
       </c>
       <c r="C26">
-        <v>0.749</v>
+        <v>0.751</v>
       </c>
       <c r="D26">
-        <v>0.029</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SWIID-GINI-DISP</t>
+          <t>UNDP-HDI-GII-LFPR-M</t>
         </is>
       </c>
       <c r="B27">
-        <v>121</v>
+        <v>24</v>
       </c>
       <c r="C27">
-        <v>0.514</v>
+        <v>0.292</v>
       </c>
       <c r="D27">
-        <v>0.027</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IMF-GDD-CG</t>
+          <t>WB-WDI-SL-EMP-TOTL-SP-FE-NE-ZS</t>
         </is>
       </c>
       <c r="B28">
-        <v>12</v>
+        <v>452</v>
       </c>
       <c r="C28">
-        <v>0.442</v>
+        <v>0.983</v>
       </c>
       <c r="D28">
-        <v>0.021</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>WB-WDI-SL-EMP-TOTL-SP-NE-ZS</t>
+          <t>WB-CWON-NFA-PC</t>
         </is>
       </c>
       <c r="B29">
-        <v>422</v>
+        <v>445</v>
       </c>
       <c r="C29">
-        <v>0.971</v>
+        <v>0.572</v>
       </c>
       <c r="D29">
-        <v>0.02</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>WB-WDI-GDP-ZG</t>
+          <t>WB-WDI-SL-EMP-TOTL-SP-NE-ZS</t>
         </is>
       </c>
       <c r="B30">
-        <v>6</v>
+        <v>422</v>
       </c>
       <c r="C30">
-        <v>0.654</v>
+        <v>0.968</v>
       </c>
       <c r="D30">
-        <v>0.017</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>WB-WDI-SL-EMP-TOTL-SP-FE-NE-ZS</t>
+          <t>UNDP-HDI-GDI-GNI-PC-F</t>
         </is>
       </c>
       <c r="B31">
-        <v>452</v>
+        <v>24</v>
       </c>
       <c r="C31">
-        <v>0.98</v>
+        <v>0.643</v>
       </c>
       <c r="D31">
-        <v>0.008999999999999999</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>UNDP-HDI-GDI-GNI-PC-F</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>24</v>
-      </c>
-      <c r="C32">
-        <v>0.157</v>
-      </c>
-      <c r="D32">
-        <v>0.003</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>WB-CWON-NFA-PC</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>445</v>
-      </c>
-      <c r="C33">
-        <v>0.525</v>
-      </c>
-      <c r="D33">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
     </row>
   </sheetData>
